--- a/Documentation/Submission/CU_eventos_completo.xlsx
+++ b/Documentation/Submission/CU_eventos_completo.xlsx
@@ -4422,7 +4422,7 @@
     <row r="1" ht="35" customHeight="1" thickBot="1">
       <c r="A1" s="118" t="inlineStr">
         <is>
-          <t>CU-003</t>
+          <t>CU-013</t>
         </is>
       </c>
       <c r="B1" s="226" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="B4" s="229" t="inlineStr">
         <is>
-          <t>Organización de eventos - HEXACORE</t>
+          <t>Sistema Integral de Gestión de Eventos</t>
         </is>
       </c>
       <c r="C4" s="147" t="n"/>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="E5" s="113" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
     <row r="1" ht="36" customHeight="1" thickBot="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CU-005</t>
+          <t>CU-015</t>
         </is>
       </c>
       <c r="B1" s="137" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="B4" s="139" t="inlineStr">
         <is>
-          <t>Organización de eventos - HEXACORE</t>
+          <t>Sistema Integral de Gestión de Eventos</t>
         </is>
       </c>
       <c r="C4" s="130" t="n"/>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
